--- a/sources/table_normalization/xlsx/environment-table25.xlsx
+++ b/sources/table_normalization/xlsx/environment-table25.xlsx
@@ -546,7 +546,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="94">
+  <cellXfs count="92">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -675,18 +675,11 @@
     <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="6" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
@@ -694,9 +687,6 @@
     <xf numFmtId="164" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="9" fontId="8" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="centerContinuous"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -708,19 +698,29 @@
     <xf numFmtId="0" fontId="6" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -1028,7 +1028,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -2162,94 +2162,94 @@
       <c r="A4" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="70"/>
-      <c r="C4" s="70"/>
-      <c r="D4" s="70"/>
-      <c r="E4" s="70"/>
-      <c r="F4" s="70"/>
-      <c r="G4" s="70"/>
-      <c r="H4" s="71"/>
-      <c r="I4" s="72" t="s">
+      <c r="B4" s="5"/>
+      <c r="C4" s="5"/>
+      <c r="D4" s="5"/>
+      <c r="E4" s="5"/>
+      <c r="F4" s="5"/>
+      <c r="G4" s="5"/>
+      <c r="H4" s="87"/>
+      <c r="I4" s="70" t="s">
         <v>3</v>
       </c>
       <c r="J4" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="K4" s="70"/>
-      <c r="L4" s="70"/>
-      <c r="M4" s="70"/>
-      <c r="N4" s="70"/>
-      <c r="O4" s="70"/>
-      <c r="P4" s="70"/>
-      <c r="Q4" s="70"/>
-      <c r="R4" s="70"/>
-      <c r="S4" s="70"/>
-      <c r="T4" s="72" t="s">
+      <c r="K4" s="5"/>
+      <c r="L4" s="5"/>
+      <c r="M4" s="5"/>
+      <c r="N4" s="5"/>
+      <c r="O4" s="5"/>
+      <c r="P4" s="5"/>
+      <c r="Q4" s="5"/>
+      <c r="R4" s="5"/>
+      <c r="S4" s="5"/>
+      <c r="T4" s="70" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:20" s="4" customFormat="1" ht="20.149999999999999" customHeight="1">
-      <c r="A5" s="73" t="s">
+      <c r="A5" s="71" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="84" t="s">
+      <c r="B5" s="79" t="s">
         <v>5</v>
       </c>
-      <c r="C5" s="84"/>
-      <c r="D5" s="84"/>
-      <c r="E5" s="84"/>
-      <c r="F5" s="84"/>
-      <c r="G5" s="84"/>
-      <c r="H5" s="84"/>
-      <c r="I5" s="85"/>
-      <c r="J5" s="76" t="s">
+      <c r="C5" s="85"/>
+      <c r="D5" s="85"/>
+      <c r="E5" s="85"/>
+      <c r="F5" s="85"/>
+      <c r="G5" s="85"/>
+      <c r="H5" s="85"/>
+      <c r="I5" s="86"/>
+      <c r="J5" s="72" t="s">
         <v>4</v>
       </c>
-      <c r="K5" s="84" t="s">
+      <c r="K5" s="79" t="s">
         <v>5</v>
       </c>
-      <c r="L5" s="84"/>
-      <c r="M5" s="84"/>
-      <c r="N5" s="84"/>
-      <c r="O5" s="84"/>
-      <c r="P5" s="84"/>
-      <c r="Q5" s="84"/>
-      <c r="R5" s="84"/>
-      <c r="S5" s="84"/>
-      <c r="T5" s="92" t="s">
+      <c r="L5" s="85"/>
+      <c r="M5" s="85"/>
+      <c r="N5" s="85"/>
+      <c r="O5" s="85"/>
+      <c r="P5" s="85"/>
+      <c r="Q5" s="85"/>
+      <c r="R5" s="85"/>
+      <c r="S5" s="85"/>
+      <c r="T5" s="88" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="6" spans="1:20" s="4" customFormat="1" ht="20.149999999999999" customHeight="1">
-      <c r="A6" s="74"/>
-      <c r="B6" s="84" t="s">
+      <c r="A6" s="37"/>
+      <c r="B6" s="85" t="s">
         <v>7</v>
       </c>
-      <c r="C6" s="84"/>
-      <c r="D6" s="84"/>
-      <c r="E6" s="84"/>
-      <c r="F6" s="84"/>
-      <c r="G6" s="84"/>
-      <c r="H6" s="84"/>
-      <c r="I6" s="85"/>
-      <c r="J6" s="74"/>
-      <c r="K6" s="84" t="s">
+      <c r="C6" s="85"/>
+      <c r="D6" s="85"/>
+      <c r="E6" s="85"/>
+      <c r="F6" s="85"/>
+      <c r="G6" s="85"/>
+      <c r="H6" s="85"/>
+      <c r="I6" s="86"/>
+      <c r="J6" s="37"/>
+      <c r="K6" s="85" t="s">
         <v>8</v>
       </c>
-      <c r="L6" s="84"/>
-      <c r="M6" s="84"/>
-      <c r="N6" s="85"/>
-      <c r="O6" s="84" t="s">
+      <c r="L6" s="85"/>
+      <c r="M6" s="85"/>
+      <c r="N6" s="86"/>
+      <c r="O6" s="85" t="s">
         <v>9</v>
       </c>
-      <c r="P6" s="84"/>
-      <c r="Q6" s="84"/>
-      <c r="R6" s="84"/>
-      <c r="S6" s="85"/>
-      <c r="T6" s="93"/>
+      <c r="P6" s="85"/>
+      <c r="Q6" s="85"/>
+      <c r="R6" s="85"/>
+      <c r="S6" s="86"/>
+      <c r="T6" s="34"/>
     </row>
     <row r="7" spans="1:20" ht="49.5" customHeight="1">
-      <c r="A7" s="75"/>
+      <c r="A7" s="83"/>
       <c r="B7" s="6" t="s">
         <v>10</v>
       </c>
@@ -2274,7 +2274,7 @@
       <c r="I7" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="J7" s="77"/>
+      <c r="J7" s="84"/>
       <c r="K7" s="6" t="s">
         <v>18</v>
       </c>
@@ -2302,7 +2302,7 @@
       <c r="S7" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="T7" s="91"/>
+      <c r="T7" s="89"/>
     </row>
     <row r="8" spans="1:20" ht="18" customHeight="1">
       <c r="A8" s="7" t="s">
@@ -3677,10 +3677,10 @@
       </c>
     </row>
     <row r="31" spans="1:21" ht="18" customHeight="1">
-      <c r="A31" s="79" t="s">
+      <c r="A31" s="74" t="s">
         <v>52</v>
       </c>
-      <c r="J31" s="80" t="s">
+      <c r="J31" s="75" t="s">
         <v>53</v>
       </c>
       <c r="K31" s="28"/>
@@ -3772,94 +3772,94 @@
       <c r="A35" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B35" s="70"/>
-      <c r="C35" s="70"/>
-      <c r="D35" s="70"/>
-      <c r="E35" s="70"/>
-      <c r="F35" s="70"/>
-      <c r="G35" s="70"/>
-      <c r="H35" s="70"/>
-      <c r="I35" s="72" t="s">
+      <c r="B35" s="5"/>
+      <c r="C35" s="5"/>
+      <c r="D35" s="5"/>
+      <c r="E35" s="5"/>
+      <c r="F35" s="5"/>
+      <c r="G35" s="5"/>
+      <c r="H35" s="5"/>
+      <c r="I35" s="70" t="s">
         <v>3</v>
       </c>
       <c r="J35" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="K35" s="70"/>
-      <c r="L35" s="70"/>
-      <c r="M35" s="70"/>
-      <c r="N35" s="70"/>
-      <c r="O35" s="70"/>
-      <c r="P35" s="70"/>
-      <c r="Q35" s="70"/>
-      <c r="R35" s="70"/>
-      <c r="S35" s="70"/>
-      <c r="T35" s="72" t="s">
+      <c r="K35" s="5"/>
+      <c r="L35" s="5"/>
+      <c r="M35" s="5"/>
+      <c r="N35" s="5"/>
+      <c r="O35" s="5"/>
+      <c r="P35" s="5"/>
+      <c r="Q35" s="5"/>
+      <c r="R35" s="5"/>
+      <c r="S35" s="5"/>
+      <c r="T35" s="70" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="36" spans="1:21" s="4" customFormat="1" ht="20.149999999999999" customHeight="1">
-      <c r="A36" s="73" t="s">
+      <c r="A36" s="71" t="s">
         <v>4</v>
       </c>
-      <c r="B36" s="84" t="s">
+      <c r="B36" s="79" t="s">
         <v>5</v>
       </c>
-      <c r="C36" s="84"/>
-      <c r="D36" s="84"/>
-      <c r="E36" s="84"/>
-      <c r="F36" s="84"/>
-      <c r="G36" s="84"/>
-      <c r="H36" s="84"/>
-      <c r="I36" s="85"/>
-      <c r="J36" s="73" t="s">
+      <c r="C36" s="85"/>
+      <c r="D36" s="85"/>
+      <c r="E36" s="85"/>
+      <c r="F36" s="85"/>
+      <c r="G36" s="85"/>
+      <c r="H36" s="85"/>
+      <c r="I36" s="86"/>
+      <c r="J36" s="71" t="s">
         <v>4</v>
       </c>
-      <c r="K36" s="84" t="s">
+      <c r="K36" s="79" t="s">
         <v>5</v>
       </c>
-      <c r="L36" s="84"/>
-      <c r="M36" s="84"/>
-      <c r="N36" s="84"/>
-      <c r="O36" s="84"/>
-      <c r="P36" s="84"/>
-      <c r="Q36" s="84"/>
-      <c r="R36" s="84"/>
-      <c r="S36" s="84"/>
-      <c r="T36" s="89" t="s">
+      <c r="L36" s="85"/>
+      <c r="M36" s="85"/>
+      <c r="N36" s="85"/>
+      <c r="O36" s="85"/>
+      <c r="P36" s="85"/>
+      <c r="Q36" s="85"/>
+      <c r="R36" s="85"/>
+      <c r="S36" s="85"/>
+      <c r="T36" s="90" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="37" spans="1:21" s="4" customFormat="1" ht="20.149999999999999" customHeight="1">
-      <c r="A37" s="74"/>
-      <c r="B37" s="84" t="s">
+      <c r="A37" s="37"/>
+      <c r="B37" s="85" t="s">
         <v>7</v>
       </c>
-      <c r="C37" s="84"/>
-      <c r="D37" s="84"/>
-      <c r="E37" s="84"/>
-      <c r="F37" s="84"/>
-      <c r="G37" s="84"/>
-      <c r="H37" s="84"/>
-      <c r="I37" s="85"/>
-      <c r="J37" s="74"/>
-      <c r="K37" s="84" t="s">
+      <c r="C37" s="85"/>
+      <c r="D37" s="85"/>
+      <c r="E37" s="85"/>
+      <c r="F37" s="85"/>
+      <c r="G37" s="85"/>
+      <c r="H37" s="85"/>
+      <c r="I37" s="86"/>
+      <c r="J37" s="37"/>
+      <c r="K37" s="85" t="s">
         <v>8</v>
       </c>
-      <c r="L37" s="84"/>
-      <c r="M37" s="84"/>
-      <c r="N37" s="85"/>
-      <c r="O37" s="84" t="s">
+      <c r="L37" s="85"/>
+      <c r="M37" s="85"/>
+      <c r="N37" s="86"/>
+      <c r="O37" s="85" t="s">
         <v>9</v>
       </c>
-      <c r="P37" s="84"/>
-      <c r="Q37" s="84"/>
-      <c r="R37" s="84"/>
-      <c r="S37" s="85"/>
-      <c r="T37" s="90"/>
+      <c r="P37" s="85"/>
+      <c r="Q37" s="85"/>
+      <c r="R37" s="85"/>
+      <c r="S37" s="86"/>
+      <c r="T37" s="91"/>
     </row>
     <row r="38" spans="1:21" ht="45" customHeight="1">
-      <c r="A38" s="75"/>
+      <c r="A38" s="83"/>
       <c r="B38" s="6" t="s">
         <v>10</v>
       </c>
@@ -3884,7 +3884,7 @@
       <c r="I38" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="J38" s="75"/>
+      <c r="J38" s="83"/>
       <c r="K38" s="6" t="s">
         <v>18</v>
       </c>
@@ -3912,7 +3912,7 @@
       <c r="S38" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="T38" s="91"/>
+      <c r="T38" s="89"/>
     </row>
     <row r="39" spans="1:21" s="15" customFormat="1" ht="18" customHeight="1">
       <c r="A39" s="34" t="s">
@@ -5179,7 +5179,7 @@
       </c>
     </row>
     <row r="62" spans="1:20" s="41" customFormat="1" ht="36.75" customHeight="1">
-      <c r="A62" s="86" t="s">
+      <c r="A62" s="80" t="s">
         <v>6</v>
       </c>
       <c r="B62" s="51">
@@ -5214,7 +5214,7 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="J62" s="86" t="s">
+      <c r="J62" s="80" t="s">
         <v>6</v>
       </c>
       <c r="K62" s="51">
@@ -5259,7 +5259,7 @@
       </c>
     </row>
     <row r="63" spans="1:20" ht="30" customHeight="1">
-      <c r="A63" s="87" t="s">
+      <c r="A63" s="81" t="s">
         <v>79</v>
       </c>
       <c r="B63" s="52">
@@ -5292,7 +5292,7 @@
       <c r="I63" s="52">
         <v>0</v>
       </c>
-      <c r="J63" s="87" t="s">
+      <c r="J63" s="81" t="s">
         <v>79</v>
       </c>
       <c r="K63" s="52">
@@ -5336,7 +5336,7 @@
       </c>
     </row>
     <row r="64" spans="1:20" ht="30" customHeight="1">
-      <c r="A64" s="87" t="s">
+      <c r="A64" s="81" t="s">
         <v>80</v>
       </c>
       <c r="B64" s="53">
@@ -5368,7 +5368,7 @@
       <c r="I64" s="54" t="s">
         <v>81</v>
       </c>
-      <c r="J64" s="87" t="s">
+      <c r="J64" s="81" t="s">
         <v>80</v>
       </c>
       <c r="K64" s="53">
@@ -5412,7 +5412,7 @@
       </c>
     </row>
     <row r="65" spans="1:20" ht="30" customHeight="1">
-      <c r="A65" s="87" t="s">
+      <c r="A65" s="81" t="s">
         <v>82</v>
       </c>
       <c r="B65" s="55">
@@ -5445,7 +5445,7 @@
       <c r="I65" s="55">
         <v>0</v>
       </c>
-      <c r="J65" s="87" t="s">
+      <c r="J65" s="81" t="s">
         <v>82</v>
       </c>
       <c r="K65" s="55">
@@ -5489,7 +5489,7 @@
       </c>
     </row>
     <row r="66" spans="1:20" ht="17.5">
-      <c r="A66" s="88" t="s">
+      <c r="A66" s="82" t="s">
         <v>83</v>
       </c>
       <c r="B66" s="57">
@@ -5516,7 +5516,7 @@
       <c r="I66" s="52">
         <v>0</v>
       </c>
-      <c r="J66" s="88" t="s">
+      <c r="J66" s="82" t="s">
         <v>83</v>
       </c>
       <c r="K66" s="57">
@@ -5560,7 +5560,7 @@
       <c r="G67" s="61"/>
       <c r="H67" s="61"/>
       <c r="I67" s="61"/>
-      <c r="J67" s="80" t="s">
+      <c r="J67" s="75" t="s">
         <v>53</v>
       </c>
       <c r="K67" s="60"/>
@@ -5575,15 +5575,15 @@
       <c r="T67" s="60"/>
     </row>
     <row r="68" spans="1:20" ht="17.5">
-      <c r="A68" s="78" t="s">
+      <c r="A68" s="73" t="s">
         <v>84</v>
       </c>
-      <c r="J68" s="78" t="s">
+      <c r="J68" s="73" t="s">
         <v>84</v>
       </c>
     </row>
     <row r="69" spans="1:20" ht="17.5">
-      <c r="A69" s="79" t="s">
+      <c r="A69" s="74" t="s">
         <v>52</v>
       </c>
       <c r="K69" s="62"/>
@@ -5598,7 +5598,7 @@
     </row>
     <row r="70" spans="1:20" ht="17.5">
       <c r="A70" s="4"/>
-      <c r="K70" s="81" t="s">
+      <c r="K70" s="76" t="s">
         <v>85</v>
       </c>
       <c r="M70" s="62"/>
@@ -5613,7 +5613,7 @@
     <row r="71" spans="1:20">
       <c r="B71" s="64"/>
       <c r="D71" s="63"/>
-      <c r="L71" s="82">
+      <c r="L71" s="77">
         <f>SUM(K62:N62)</f>
         <v>310033</v>
       </c>
@@ -5621,7 +5621,7 @@
     <row r="72" spans="1:20" ht="15.5">
       <c r="C72" s="65"/>
       <c r="D72" s="66"/>
-      <c r="L72" s="83">
+      <c r="L72" s="78">
         <f>SUM(K62:O62)/T62</f>
         <v>0.78215400650421174</v>
       </c>
